--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L3" s="3" t="n">

--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L4" s="3" t="n">

--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L6" s="3" t="n">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L7" s="3" t="n">

--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L9" s="3" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L11" s="3" t="n">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L12" s="3" t="n">

--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L14" s="3" t="n">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L16" s="3" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L17" s="3" t="n">

--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L15" s="3" t="n">

--- a/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
+++ b/Mundial 2026 - Reporte Maestro de Simulaciones.xlsx
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>E</t>
         </is>
       </c>
       <c r="L22" s="3" t="n">
